--- a/artfynd/A 55279-2025 artfynd.xlsx
+++ b/artfynd/A 55279-2025 artfynd.xlsx
@@ -1300,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129960347</v>
+        <v>129959101</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,31 +1311,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574039</v>
+        <v>573861</v>
       </c>
       <c r="R8" t="n">
-        <v>6738602</v>
+        <v>6738734</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129959101</v>
+        <v>129960347</v>
       </c>
       <c r="B9" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,31 +1427,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573861</v>
+        <v>574039</v>
       </c>
       <c r="R9" t="n">
-        <v>6738734</v>
+        <v>6738602</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2328,10 +2328,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129965765</v>
+        <v>129959721</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,37 +2339,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573922</v>
+        <v>573861</v>
       </c>
       <c r="R18" t="n">
-        <v>6738567</v>
+        <v>6738734</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2396,92 +2405,87 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129960128</v>
+        <v>129965765</v>
       </c>
       <c r="B19" t="n">
-        <v>97665</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574039</v>
+        <v>573922</v>
       </c>
       <c r="R19" t="n">
-        <v>6738602</v>
+        <v>6738567</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,81 +2512,77 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129959721</v>
+        <v>129960128</v>
       </c>
       <c r="B20" t="n">
-        <v>78841</v>
+        <v>97665</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>573861</v>
+        <v>574039</v>
       </c>
       <c r="R20" t="n">
-        <v>6738734</v>
+        <v>6738602</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129965762</v>
+        <v>129965766</v>
       </c>
       <c r="B24" t="n">
         <v>79084</v>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>573793</v>
+        <v>574017</v>
       </c>
       <c r="R24" t="n">
-        <v>6738585</v>
+        <v>6738609</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3071,7 +3071,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129965766</v>
+        <v>129965762</v>
       </c>
       <c r="B25" t="n">
         <v>79084</v>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574017</v>
+        <v>573793</v>
       </c>
       <c r="R25" t="n">
-        <v>6738609</v>
+        <v>6738585</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3363,32 +3363,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129965741</v>
+        <v>129965748</v>
       </c>
       <c r="B28" t="n">
-        <v>97671</v>
+        <v>78842</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574026</v>
+        <v>573612</v>
       </c>
       <c r="R28" t="n">
-        <v>6738550</v>
+        <v>6738861</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3460,32 +3460,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129965748</v>
+        <v>129965741</v>
       </c>
       <c r="B29" t="n">
-        <v>78842</v>
+        <v>97671</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>573612</v>
+        <v>574026</v>
       </c>
       <c r="R29" t="n">
-        <v>6738861</v>
+        <v>6738550</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129965764</v>
+        <v>129965768</v>
       </c>
       <c r="B31" t="n">
         <v>79084</v>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>573898</v>
+        <v>573802</v>
       </c>
       <c r="R31" t="n">
-        <v>6738621</v>
+        <v>6738732</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129965768</v>
+        <v>129965764</v>
       </c>
       <c r="B32" t="n">
         <v>79084</v>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>573802</v>
+        <v>573898</v>
       </c>
       <c r="R32" t="n">
-        <v>6738732</v>
+        <v>6738621</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129965767</v>
+        <v>129965769</v>
       </c>
       <c r="B37" t="n">
         <v>79084</v>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>573893</v>
+        <v>573745</v>
       </c>
       <c r="R37" t="n">
-        <v>6738657</v>
+        <v>6738790</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129965769</v>
+        <v>129965767</v>
       </c>
       <c r="B39" t="n">
         <v>79084</v>
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>573745</v>
+        <v>573893</v>
       </c>
       <c r="R39" t="n">
-        <v>6738790</v>
+        <v>6738657</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>

--- a/artfynd/A 55279-2025 artfynd.xlsx
+++ b/artfynd/A 55279-2025 artfynd.xlsx
@@ -990,57 +990,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129960414</v>
+        <v>129965757</v>
       </c>
       <c r="B5" t="n">
-        <v>97668</v>
+        <v>78841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573945</v>
+        <v>574070</v>
       </c>
       <c r="R5" t="n">
-        <v>6738585</v>
+        <v>6738621</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,19 +1058,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,22 +1075,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129965757</v>
+        <v>129965746</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>78842</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574070</v>
+        <v>573966</v>
       </c>
       <c r="R6" t="n">
-        <v>6738621</v>
+        <v>6738665</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1203,48 +1184,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129965746</v>
+        <v>129960414</v>
       </c>
       <c r="B7" t="n">
-        <v>78842</v>
+        <v>97668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573966</v>
+        <v>573945</v>
       </c>
       <c r="R7" t="n">
-        <v>6738665</v>
+        <v>6738585</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1271,9 +1261,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1288,22 +1288,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129959101</v>
+        <v>129960347</v>
       </c>
       <c r="B8" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,31 +1311,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573861</v>
+        <v>574039</v>
       </c>
       <c r="R8" t="n">
-        <v>6738734</v>
+        <v>6738602</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129960347</v>
+        <v>129959101</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,31 +1427,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574039</v>
+        <v>573861</v>
       </c>
       <c r="R9" t="n">
-        <v>6738602</v>
+        <v>6738734</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129965749</v>
+        <v>129965747</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>78842</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574026</v>
+        <v>573690</v>
       </c>
       <c r="R10" t="n">
-        <v>6738550</v>
+        <v>6738836</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,32 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129965747</v>
+        <v>129965749</v>
       </c>
       <c r="B11" t="n">
-        <v>78842</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573690</v>
+        <v>574026</v>
       </c>
       <c r="R11" t="n">
-        <v>6738836</v>
+        <v>6738550</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129965766</v>
+        <v>129965762</v>
       </c>
       <c r="B24" t="n">
         <v>79084</v>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574017</v>
+        <v>573793</v>
       </c>
       <c r="R24" t="n">
-        <v>6738609</v>
+        <v>6738585</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3071,7 +3071,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129965762</v>
+        <v>129965766</v>
       </c>
       <c r="B25" t="n">
         <v>79084</v>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>573793</v>
+        <v>574017</v>
       </c>
       <c r="R25" t="n">
-        <v>6738585</v>
+        <v>6738609</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3363,32 +3363,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129965748</v>
+        <v>129965741</v>
       </c>
       <c r="B28" t="n">
-        <v>78842</v>
+        <v>97671</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>573612</v>
+        <v>574026</v>
       </c>
       <c r="R28" t="n">
-        <v>6738861</v>
+        <v>6738550</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3460,32 +3460,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129965741</v>
+        <v>129965748</v>
       </c>
       <c r="B29" t="n">
-        <v>97671</v>
+        <v>78842</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574026</v>
+        <v>573612</v>
       </c>
       <c r="R29" t="n">
-        <v>6738550</v>
+        <v>6738861</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129965768</v>
+        <v>129965764</v>
       </c>
       <c r="B31" t="n">
         <v>79084</v>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>573802</v>
+        <v>573898</v>
       </c>
       <c r="R31" t="n">
-        <v>6738732</v>
+        <v>6738621</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129965764</v>
+        <v>129965768</v>
       </c>
       <c r="B32" t="n">
         <v>79084</v>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>573898</v>
+        <v>573802</v>
       </c>
       <c r="R32" t="n">
-        <v>6738621</v>
+        <v>6738732</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4044,10 +4044,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129965763</v>
+        <v>129965753</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,21 +4055,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>573855</v>
+        <v>573818</v>
       </c>
       <c r="R35" t="n">
-        <v>6738592</v>
+        <v>6738603</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4123,7 +4123,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4142,10 +4141,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129965753</v>
+        <v>129965763</v>
       </c>
       <c r="B36" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,21 +4152,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4177,10 +4176,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>573818</v>
+        <v>573855</v>
       </c>
       <c r="R36" t="n">
-        <v>6738603</v>
+        <v>6738592</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4221,6 +4220,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129965769</v>
+        <v>129965767</v>
       </c>
       <c r="B37" t="n">
         <v>79084</v>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>573745</v>
+        <v>573893</v>
       </c>
       <c r="R37" t="n">
-        <v>6738790</v>
+        <v>6738657</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129965767</v>
+        <v>129965769</v>
       </c>
       <c r="B39" t="n">
         <v>79084</v>
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>573893</v>
+        <v>573745</v>
       </c>
       <c r="R39" t="n">
-        <v>6738657</v>
+        <v>6738790</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>

--- a/artfynd/A 55279-2025 artfynd.xlsx
+++ b/artfynd/A 55279-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129965755</v>
+        <v>129965760</v>
       </c>
       <c r="B2" t="n">
-        <v>78841</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573875</v>
+        <v>573918</v>
       </c>
       <c r="R2" t="n">
-        <v>6738466</v>
+        <v>6738527</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129965760</v>
+        <v>129965755</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573918</v>
+        <v>573875</v>
       </c>
       <c r="R3" t="n">
-        <v>6738527</v>
+        <v>6738466</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>129958787</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,48 +990,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129965757</v>
+        <v>129960414</v>
       </c>
       <c r="B5" t="n">
-        <v>78841</v>
+        <v>97671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574070</v>
+        <v>573945</v>
       </c>
       <c r="R5" t="n">
-        <v>6738621</v>
+        <v>6738585</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1058,9 +1067,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,12 +1094,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1090,7 +1109,7 @@
         <v>129965746</v>
       </c>
       <c r="B6" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,57 +1203,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129960414</v>
+        <v>129965757</v>
       </c>
       <c r="B7" t="n">
-        <v>97668</v>
+        <v>78844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573945</v>
+        <v>574070</v>
       </c>
       <c r="R7" t="n">
-        <v>6738585</v>
+        <v>6738621</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,19 +1271,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1288,22 +1288,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129960347</v>
+        <v>129959101</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,31 +1311,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574039</v>
+        <v>573861</v>
       </c>
       <c r="R8" t="n">
-        <v>6738602</v>
+        <v>6738734</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129959101</v>
+        <v>129960347</v>
       </c>
       <c r="B9" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,31 +1427,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573861</v>
+        <v>574039</v>
       </c>
       <c r="R9" t="n">
-        <v>6738734</v>
+        <v>6738602</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,7 +1535,7 @@
         <v>129965747</v>
       </c>
       <c r="B10" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129965749</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129965736</v>
+        <v>129959968</v>
       </c>
       <c r="B12" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,37 +1737,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574018</v>
+        <v>574074</v>
       </c>
       <c r="R12" t="n">
-        <v>6738557</v>
+        <v>6738583</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,9 +1803,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1811,22 +1830,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129959968</v>
+        <v>129965771</v>
       </c>
       <c r="B13" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,46 +1853,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574074</v>
+        <v>573627</v>
       </c>
       <c r="R13" t="n">
-        <v>6738583</v>
+        <v>6738750</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1900,71 +1910,62 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129965771</v>
+        <v>129965751</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,7 +1978,7 @@
         <v>573627</v>
       </c>
       <c r="R14" t="n">
-        <v>6738750</v>
+        <v>6738845</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2018,7 +2019,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2037,32 +2037,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129965751</v>
+        <v>129965744</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>78845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573627</v>
+        <v>574016</v>
       </c>
       <c r="R15" t="n">
-        <v>6738845</v>
+        <v>6738552</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2134,10 +2134,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129965734</v>
+        <v>129965765</v>
       </c>
       <c r="B16" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,21 +2145,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573877</v>
+        <v>573922</v>
       </c>
       <c r="R16" t="n">
-        <v>6738464</v>
+        <v>6738567</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2213,6 +2213,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2231,10 +2232,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129965744</v>
+        <v>129959721</v>
       </c>
       <c r="B17" t="n">
-        <v>78842</v>
+        <v>78844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2242,37 +2243,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574016</v>
+        <v>573861</v>
       </c>
       <c r="R17" t="n">
-        <v>6738552</v>
+        <v>6738734</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2299,9 +2309,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,54 +2336,59 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129959721</v>
+        <v>129960128</v>
       </c>
       <c r="B18" t="n">
-        <v>78841</v>
+        <v>97668</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2372,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573861</v>
+        <v>574039</v>
       </c>
       <c r="R18" t="n">
-        <v>6738734</v>
+        <v>6738602</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2444,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129965765</v>
+        <v>129960228</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2472,20 +2497,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>573922</v>
+        <v>574033</v>
       </c>
       <c r="R19" t="n">
-        <v>6738567</v>
+        <v>6738647</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,92 +2546,87 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129960128</v>
+        <v>129965758</v>
       </c>
       <c r="B20" t="n">
-        <v>97665</v>
+        <v>78844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574039</v>
+        <v>573893</v>
       </c>
       <c r="R20" t="n">
-        <v>6738602</v>
+        <v>6738674</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2624,19 +2653,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2651,22 +2670,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129965737</v>
+        <v>129965766</v>
       </c>
       <c r="B21" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,21 +2693,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2717,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574015</v>
+        <v>574017</v>
       </c>
       <c r="R21" t="n">
-        <v>6738717</v>
+        <v>6738609</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2742,6 +2761,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2760,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129965758</v>
+        <v>129965762</v>
       </c>
       <c r="B22" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2795,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>573893</v>
+        <v>573793</v>
       </c>
       <c r="R22" t="n">
-        <v>6738674</v>
+        <v>6738585</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2839,6 +2859,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2857,57 +2878,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129960228</v>
+        <v>129965750</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574033</v>
+        <v>574018</v>
       </c>
       <c r="R23" t="n">
-        <v>6738647</v>
+        <v>6738616</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2934,19 +2946,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2961,22 +2963,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129965762</v>
+        <v>129965743</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,21 +2986,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3008,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>573793</v>
+        <v>573814</v>
       </c>
       <c r="R24" t="n">
-        <v>6738585</v>
+        <v>6738462</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3052,7 +3054,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3071,32 +3072,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129965766</v>
+        <v>129965741</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>97674</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3106,10 +3107,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574017</v>
+        <v>574026</v>
       </c>
       <c r="R25" t="n">
-        <v>6738609</v>
+        <v>6738550</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3150,7 +3151,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3169,32 +3169,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129965750</v>
+        <v>129965748</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>78845</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574018</v>
+        <v>573612</v>
       </c>
       <c r="R26" t="n">
-        <v>6738616</v>
+        <v>6738861</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129965743</v>
+        <v>129965756</v>
       </c>
       <c r="B27" t="n">
-        <v>78842</v>
+        <v>78844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>573814</v>
+        <v>573815</v>
       </c>
       <c r="R27" t="n">
-        <v>6738462</v>
+        <v>6738469</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3363,32 +3363,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129965741</v>
+        <v>129965768</v>
       </c>
       <c r="B28" t="n">
-        <v>97671</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574026</v>
+        <v>573802</v>
       </c>
       <c r="R28" t="n">
-        <v>6738550</v>
+        <v>6738732</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3442,6 +3442,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3460,10 +3461,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129965748</v>
+        <v>129965745</v>
       </c>
       <c r="B29" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3495,10 +3496,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>573612</v>
+        <v>574015</v>
       </c>
       <c r="R29" t="n">
-        <v>6738861</v>
+        <v>6738720</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3557,10 +3558,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129965756</v>
+        <v>129965764</v>
       </c>
       <c r="B30" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3568,21 +3569,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3592,10 +3593,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>573815</v>
+        <v>573898</v>
       </c>
       <c r="R30" t="n">
-        <v>6738469</v>
+        <v>6738621</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3636,6 +3637,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3654,10 +3656,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129965764</v>
+        <v>129965763</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3689,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>573898</v>
+        <v>573855</v>
       </c>
       <c r="R31" t="n">
-        <v>6738621</v>
+        <v>6738592</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3752,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129965768</v>
+        <v>129965753</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3763,21 +3765,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3787,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>573802</v>
+        <v>573818</v>
       </c>
       <c r="R32" t="n">
-        <v>6738732</v>
+        <v>6738603</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3831,7 +3833,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3850,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129965745</v>
+        <v>129965767</v>
       </c>
       <c r="B33" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3861,21 +3862,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3885,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574015</v>
+        <v>573893</v>
       </c>
       <c r="R33" t="n">
-        <v>6738720</v>
+        <v>6738657</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3929,6 +3930,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3947,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129965735</v>
+        <v>129965770</v>
       </c>
       <c r="B34" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3958,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3982,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>573815</v>
+        <v>573686</v>
       </c>
       <c r="R34" t="n">
-        <v>6738469</v>
+        <v>6738830</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4026,6 +4028,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4044,10 +4047,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129965753</v>
+        <v>129965769</v>
       </c>
       <c r="B35" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,21 +4058,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4082,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>573818</v>
+        <v>573745</v>
       </c>
       <c r="R35" t="n">
-        <v>6738603</v>
+        <v>6738790</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4123,6 +4126,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4141,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129965763</v>
+        <v>130009885</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4152,37 +4156,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kojmyran, Dlr</t>
+          <t>Kojmyran Dlr, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>573855</v>
+        <v>573875</v>
       </c>
       <c r="R36" t="n">
-        <v>6738592</v>
+        <v>6738467</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4209,9 +4216,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4227,60 +4244,68 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129965767</v>
+        <v>130009800</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>56930</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kojmyran, Dlr</t>
+          <t>Kojmyran Dlr, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>573893</v>
+        <v>573920</v>
       </c>
       <c r="R37" t="n">
-        <v>6738657</v>
+        <v>6738446</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4307,40 +4332,54 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Väldigt tjocka, låg på båda sidor på stenen och i lingonriset nedanför. Väster om Kojmyran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129965770</v>
+        <v>130009812</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4366,19 +4405,22 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kojmyran, Dlr</t>
+          <t>Kojmyran Dlr, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>573686</v>
+        <v>573836</v>
       </c>
       <c r="R38" t="n">
-        <v>6738830</v>
+        <v>6738664</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4405,9 +4447,24 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På flera tallar med brandljud</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4423,22 +4480,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129965769</v>
+        <v>130009809</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4464,19 +4521,22 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kojmyran, Dlr</t>
+          <t>Kojmyran Dlr, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>573745</v>
+        <v>573882</v>
       </c>
       <c r="R39" t="n">
-        <v>6738790</v>
+        <v>6738541</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4503,9 +4563,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4521,15 +4591,2269 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130009811</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>573888</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6738654</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tyvärr tog jag inget foto</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129965736</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kojmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>574018</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6738557</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
           <t>Erik Danielsson</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AX41" t="inlineStr">
         <is>
           <t>Erik Danielsson</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130009803</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>573770</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6738714</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129965734</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kojmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>573877</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6738464</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129965737</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kojmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>574015</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6738717</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130009806</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>573915</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6738548</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>uppskattat antal</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130009808</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>573923</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6738562</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Delvis snö, uppskattat antal.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130009880</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>573818</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6738607</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130009817</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>573876</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6738460</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130009802</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>573934</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6738551</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130009804</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97668</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>573918</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6738545</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130009905</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91569</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>573896</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6738545</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130009906</v>
+      </c>
+      <c r="B52" t="n">
+        <v>56930</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>573857</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6738656</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130009810</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>573896</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6738553</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Vackert draperad gran</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130009893</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>573916</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6738552</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130009882</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>573810</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6738459</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>I äldre björk</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130009815</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92887</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>573896</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6738426</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130009895</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78753</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>353</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>573923</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6738609</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129965735</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kojmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>573815</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6738469</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130009805</v>
+      </c>
+      <c r="B59" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kojmyran Dlr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>573876</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6738509</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55279-2025 artfynd.xlsx
+++ b/artfynd/A 55279-2025 artfynd.xlsx
@@ -990,57 +990,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129960414</v>
+        <v>129965757</v>
       </c>
       <c r="B5" t="n">
-        <v>97671</v>
+        <v>78844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573945</v>
+        <v>574070</v>
       </c>
       <c r="R5" t="n">
-        <v>6738585</v>
+        <v>6738621</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,19 +1058,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,60 +1075,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129965746</v>
+        <v>129960414</v>
       </c>
       <c r="B6" t="n">
-        <v>78845</v>
+        <v>97671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573966</v>
+        <v>573945</v>
       </c>
       <c r="R6" t="n">
-        <v>6738665</v>
+        <v>6738585</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,9 +1164,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129965757</v>
+        <v>129965746</v>
       </c>
       <c r="B7" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574070</v>
+        <v>573966</v>
       </c>
       <c r="R7" t="n">
-        <v>6738621</v>
+        <v>6738665</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129959101</v>
+        <v>129960347</v>
       </c>
       <c r="B8" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,31 +1311,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573861</v>
+        <v>574039</v>
       </c>
       <c r="R8" t="n">
-        <v>6738734</v>
+        <v>6738602</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129960347</v>
+        <v>129959101</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,31 +1427,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574039</v>
+        <v>573861</v>
       </c>
       <c r="R9" t="n">
-        <v>6738602</v>
+        <v>6738734</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3072,32 +3072,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129965741</v>
+        <v>129965748</v>
       </c>
       <c r="B25" t="n">
-        <v>97674</v>
+        <v>78845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574026</v>
+        <v>573612</v>
       </c>
       <c r="R25" t="n">
-        <v>6738550</v>
+        <v>6738861</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3169,32 +3169,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129965748</v>
+        <v>129965741</v>
       </c>
       <c r="B26" t="n">
-        <v>78845</v>
+        <v>97674</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>573612</v>
+        <v>574026</v>
       </c>
       <c r="R26" t="n">
-        <v>6738861</v>
+        <v>6738550</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129965768</v>
+        <v>129965764</v>
       </c>
       <c r="B28" t="n">
         <v>79087</v>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>573802</v>
+        <v>573898</v>
       </c>
       <c r="R28" t="n">
-        <v>6738732</v>
+        <v>6738621</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129965745</v>
+        <v>129965768</v>
       </c>
       <c r="B29" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574015</v>
+        <v>573802</v>
       </c>
       <c r="R29" t="n">
-        <v>6738720</v>
+        <v>6738732</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3540,6 +3540,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3558,10 +3559,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129965764</v>
+        <v>129965745</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3569,21 +3570,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3593,10 +3594,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>573898</v>
+        <v>574015</v>
       </c>
       <c r="R30" t="n">
-        <v>6738621</v>
+        <v>6738720</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3637,7 +3638,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55279-2025 artfynd.xlsx
+++ b/artfynd/A 55279-2025 artfynd.xlsx
@@ -1532,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129965747</v>
+        <v>129965749</v>
       </c>
       <c r="B10" t="n">
-        <v>78845</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573690</v>
+        <v>574026</v>
       </c>
       <c r="R10" t="n">
-        <v>6738836</v>
+        <v>6738550</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,32 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129965749</v>
+        <v>129965747</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>78845</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574026</v>
+        <v>573690</v>
       </c>
       <c r="R11" t="n">
-        <v>6738550</v>
+        <v>6738836</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -2134,48 +2134,62 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129965765</v>
+        <v>129960128</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>97668</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573922</v>
+        <v>574039</v>
       </c>
       <c r="R16" t="n">
-        <v>6738567</v>
+        <v>6738602</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2202,30 +2216,39 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2348,62 +2371,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129960128</v>
+        <v>129965765</v>
       </c>
       <c r="B18" t="n">
-        <v>97668</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574039</v>
+        <v>573922</v>
       </c>
       <c r="R18" t="n">
-        <v>6738602</v>
+        <v>6738567</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2430,39 +2439,30 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2682,7 +2682,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129965766</v>
+        <v>129965762</v>
       </c>
       <c r="B21" t="n">
         <v>79087</v>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574017</v>
+        <v>573793</v>
       </c>
       <c r="R21" t="n">
-        <v>6738609</v>
+        <v>6738585</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129965762</v>
+        <v>129965743</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2791,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>573793</v>
+        <v>573814</v>
       </c>
       <c r="R22" t="n">
-        <v>6738585</v>
+        <v>6738462</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2859,7 +2859,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2878,32 +2877,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129965750</v>
+        <v>129965766</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2913,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574018</v>
+        <v>574017</v>
       </c>
       <c r="R23" t="n">
-        <v>6738616</v>
+        <v>6738609</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2957,6 +2956,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2975,32 +2975,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129965743</v>
+        <v>129965750</v>
       </c>
       <c r="B24" t="n">
-        <v>78845</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>573814</v>
+        <v>574018</v>
       </c>
       <c r="R24" t="n">
-        <v>6738462</v>
+        <v>6738616</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129965764</v>
+        <v>129965768</v>
       </c>
       <c r="B28" t="n">
         <v>79087</v>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>573898</v>
+        <v>573802</v>
       </c>
       <c r="R28" t="n">
-        <v>6738621</v>
+        <v>6738732</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129965768</v>
+        <v>129965745</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>573802</v>
+        <v>574015</v>
       </c>
       <c r="R29" t="n">
-        <v>6738732</v>
+        <v>6738720</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3540,7 +3540,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3559,10 +3558,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129965745</v>
+        <v>129965764</v>
       </c>
       <c r="B30" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,21 +3569,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3594,10 +3593,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574015</v>
+        <v>573898</v>
       </c>
       <c r="R30" t="n">
-        <v>6738720</v>
+        <v>6738621</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3638,6 +3637,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -6533,10 +6533,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130009895</v>
+        <v>129965735</v>
       </c>
       <c r="B57" t="n">
-        <v>78753</v>
+        <v>79706</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6544,21 +6544,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6567,17 +6567,17 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kojmyran Dlr, Dlr</t>
+          <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>573923</v>
+        <v>573815</v>
       </c>
       <c r="R57" t="n">
-        <v>6738609</v>
+        <v>6738469</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6604,50 +6604,39 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129965735</v>
+        <v>130009895</v>
       </c>
       <c r="B58" t="n">
-        <v>79706</v>
+        <v>78753</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6655,21 +6644,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6678,17 +6667,17 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kojmyran, Dlr</t>
+          <t>Kojmyran Dlr, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>573815</v>
+        <v>573923</v>
       </c>
       <c r="R58" t="n">
-        <v>6738469</v>
+        <v>6738609</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6715,29 +6704,40 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 55279-2025 artfynd.xlsx
+++ b/artfynd/A 55279-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129965760</v>
+        <v>129965755</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>78845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573918</v>
+        <v>573875</v>
       </c>
       <c r="R2" t="n">
-        <v>6738527</v>
+        <v>6738466</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129965755</v>
+        <v>129965760</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573875</v>
+        <v>573918</v>
       </c>
       <c r="R3" t="n">
-        <v>6738466</v>
+        <v>6738527</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -993,7 +993,7 @@
         <v>129965757</v>
       </c>
       <c r="B5" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>129960414</v>
       </c>
       <c r="B6" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>129965746</v>
       </c>
       <c r="B7" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>129960347</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>129959101</v>
       </c>
       <c r="B9" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129965747</v>
       </c>
       <c r="B11" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>129959968</v>
       </c>
       <c r="B12" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129965771</v>
+        <v>129965751</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1880,7 +1880,7 @@
         <v>573627</v>
       </c>
       <c r="R13" t="n">
-        <v>6738750</v>
+        <v>6738845</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1921,7 +1921,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1940,32 +1939,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129965751</v>
+        <v>129965771</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1978,7 +1977,7 @@
         <v>573627</v>
       </c>
       <c r="R14" t="n">
-        <v>6738845</v>
+        <v>6738750</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2019,6 +2018,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>129965744</v>
       </c>
       <c r="B15" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,47 +2134,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129960128</v>
+        <v>129959721</v>
       </c>
       <c r="B16" t="n">
-        <v>97668</v>
+        <v>78845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2183,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574039</v>
+        <v>573861</v>
       </c>
       <c r="R16" t="n">
-        <v>6738602</v>
+        <v>6738734</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2255,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129959721</v>
+        <v>129965765</v>
       </c>
       <c r="B17" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2266,46 +2261,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573861</v>
+        <v>573922</v>
       </c>
       <c r="R17" t="n">
-        <v>6738734</v>
+        <v>6738567</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2332,87 +2318,92 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129965765</v>
+        <v>129960128</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>97669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573922</v>
+        <v>574039</v>
       </c>
       <c r="R18" t="n">
-        <v>6738567</v>
+        <v>6738602</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2439,40 +2430,49 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129960228</v>
+        <v>129965758</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,46 +2480,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574033</v>
+        <v>573893</v>
       </c>
       <c r="R19" t="n">
-        <v>6738647</v>
+        <v>6738674</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2546,19 +2537,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2573,22 +2554,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129965758</v>
+        <v>129960228</v>
       </c>
       <c r="B20" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,37 +2577,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>573893</v>
+        <v>574033</v>
       </c>
       <c r="R20" t="n">
-        <v>6738674</v>
+        <v>6738647</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2653,9 +2643,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2670,12 +2670,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
         <v>129965762</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129965743</v>
+        <v>129965766</v>
       </c>
       <c r="B22" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2791,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>573814</v>
+        <v>574017</v>
       </c>
       <c r="R22" t="n">
-        <v>6738462</v>
+        <v>6738609</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2859,6 +2859,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2877,32 +2878,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129965766</v>
+        <v>129965750</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2912,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574017</v>
+        <v>574018</v>
       </c>
       <c r="R23" t="n">
-        <v>6738609</v>
+        <v>6738616</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2956,7 +2957,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2975,32 +2975,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129965750</v>
+        <v>129965743</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>78846</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574018</v>
+        <v>573814</v>
       </c>
       <c r="R24" t="n">
-        <v>6738616</v>
+        <v>6738462</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3072,32 +3072,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129965748</v>
+        <v>129965741</v>
       </c>
       <c r="B25" t="n">
-        <v>78845</v>
+        <v>97675</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>573612</v>
+        <v>574026</v>
       </c>
       <c r="R25" t="n">
-        <v>6738861</v>
+        <v>6738550</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3169,32 +3169,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129965741</v>
+        <v>129965748</v>
       </c>
       <c r="B26" t="n">
-        <v>97674</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574026</v>
+        <v>573612</v>
       </c>
       <c r="R26" t="n">
-        <v>6738550</v>
+        <v>6738861</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3269,7 +3269,7 @@
         <v>129965756</v>
       </c>
       <c r="B27" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129965768</v>
+        <v>129965764</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>573802</v>
+        <v>573898</v>
       </c>
       <c r="R28" t="n">
-        <v>6738732</v>
+        <v>6738621</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129965745</v>
+        <v>129965768</v>
       </c>
       <c r="B29" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574015</v>
+        <v>573802</v>
       </c>
       <c r="R29" t="n">
-        <v>6738720</v>
+        <v>6738732</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3540,6 +3540,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3558,10 +3559,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129965764</v>
+        <v>129965745</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3569,21 +3570,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3593,10 +3594,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>573898</v>
+        <v>574015</v>
       </c>
       <c r="R30" t="n">
-        <v>6738621</v>
+        <v>6738720</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3637,7 +3638,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129965763</v>
+        <v>129965753</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>573855</v>
+        <v>573818</v>
       </c>
       <c r="R31" t="n">
-        <v>6738592</v>
+        <v>6738603</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3735,7 +3735,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3754,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129965753</v>
+        <v>129965763</v>
       </c>
       <c r="B32" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3765,21 +3764,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3788,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>573818</v>
+        <v>573855</v>
       </c>
       <c r="R32" t="n">
-        <v>6738603</v>
+        <v>6738592</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3833,6 +3832,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>129965767</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>129965770</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>129965769</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>130009885</v>
       </c>
       <c r="B36" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>130009812</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>130009809</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>130009811</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>129965736</v>
       </c>
       <c r="B41" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>129965734</v>
       </c>
       <c r="B43" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>129965737</v>
       </c>
       <c r="B44" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>130009806</v>
       </c>
       <c r="B45" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>130009808</v>
       </c>
       <c r="B46" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>130009880</v>
       </c>
       <c r="B47" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>130009804</v>
       </c>
       <c r="B50" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>130009905</v>
       </c>
       <c r="B51" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>130009810</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,10 +6183,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130009893</v>
+        <v>129965735</v>
       </c>
       <c r="B54" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6194,45 +6194,40 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kojmyran Dlr, Dlr</t>
+          <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>573916</v>
+        <v>573815</v>
       </c>
       <c r="R54" t="n">
-        <v>6738552</v>
+        <v>6738469</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6259,19 +6254,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6286,22 +6271,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130009882</v>
+        <v>130009895</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>78754</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6309,21 +6294,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6336,10 +6321,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>573810</v>
+        <v>573923</v>
       </c>
       <c r="R55" t="n">
-        <v>6738459</v>
+        <v>6738609</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6371,7 +6356,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6381,12 +6366,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>I äldre björk</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6414,44 +6394,36 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130009815</v>
+        <v>130009882</v>
       </c>
       <c r="B56" t="n">
-        <v>92887</v>
+        <v>79088</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -6460,10 +6432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>573896</v>
+        <v>573810</v>
       </c>
       <c r="R56" t="n">
-        <v>6738426</v>
+        <v>6738459</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6495,7 +6467,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6505,7 +6477,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>I äldre björk</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6533,51 +6510,59 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129965735</v>
+        <v>130009815</v>
       </c>
       <c r="B57" t="n">
-        <v>79706</v>
+        <v>92888</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kojmyran, Dlr</t>
+          <t>Kojmyran Dlr, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>573815</v>
+        <v>573896</v>
       </c>
       <c r="R57" t="n">
-        <v>6738469</v>
+        <v>6738426</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6604,39 +6589,50 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130009895</v>
+        <v>130009893</v>
       </c>
       <c r="B58" t="n">
-        <v>78753</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6644,26 +6640,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6671,10 +6672,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>573923</v>
+        <v>573916</v>
       </c>
       <c r="R58" t="n">
-        <v>6738609</v>
+        <v>6738552</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6706,7 +6707,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6716,7 +6717,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6725,7 +6726,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55279-2025 artfynd.xlsx
+++ b/artfynd/A 55279-2025 artfynd.xlsx
@@ -990,48 +990,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129965757</v>
+        <v>129960414</v>
       </c>
       <c r="B5" t="n">
-        <v>78845</v>
+        <v>97672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574070</v>
+        <v>573945</v>
       </c>
       <c r="R5" t="n">
-        <v>6738621</v>
+        <v>6738585</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1058,9 +1067,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,69 +1094,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129960414</v>
+        <v>129965746</v>
       </c>
       <c r="B6" t="n">
-        <v>97672</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573945</v>
+        <v>573966</v>
       </c>
       <c r="R6" t="n">
-        <v>6738585</v>
+        <v>6738665</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1164,19 +1174,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129965746</v>
+        <v>129965757</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>78845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573966</v>
+        <v>574070</v>
       </c>
       <c r="R7" t="n">
-        <v>6738665</v>
+        <v>6738621</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1532,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129965749</v>
+        <v>129965747</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574026</v>
+        <v>573690</v>
       </c>
       <c r="R10" t="n">
-        <v>6738550</v>
+        <v>6738836</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,32 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129965747</v>
+        <v>129965749</v>
       </c>
       <c r="B11" t="n">
-        <v>78846</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573690</v>
+        <v>574026</v>
       </c>
       <c r="R11" t="n">
-        <v>6738836</v>
+        <v>6738550</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130009803</v>
+        <v>129965734</v>
       </c>
       <c r="B42" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4831,45 +4831,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kojmyran Dlr, Dlr</t>
+          <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>573770</v>
+        <v>573877</v>
       </c>
       <c r="R42" t="n">
-        <v>6738714</v>
+        <v>6738464</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4896,19 +4891,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4923,22 +4908,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129965734</v>
+        <v>130009803</v>
       </c>
       <c r="B43" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4946,40 +4931,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kojmyran, Dlr</t>
+          <t>Kojmyran Dlr, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>573877</v>
+        <v>573770</v>
       </c>
       <c r="R43" t="n">
-        <v>6738464</v>
+        <v>6738714</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5006,9 +4996,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5023,12 +5023,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130009905</v>
+        <v>130009906</v>
       </c>
       <c r="B51" t="n">
-        <v>91570</v>
+        <v>56930</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5847,26 +5847,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5874,10 +5879,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>573896</v>
+        <v>573857</v>
       </c>
       <c r="R51" t="n">
-        <v>6738545</v>
+        <v>6738656</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5909,7 +5914,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5919,7 +5924,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5928,7 +5938,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5947,10 +5956,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130009906</v>
+        <v>130009905</v>
       </c>
       <c r="B52" t="n">
-        <v>56930</v>
+        <v>91570</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5958,31 +5967,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5990,10 +5994,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>573857</v>
+        <v>573896</v>
       </c>
       <c r="R52" t="n">
-        <v>6738656</v>
+        <v>6738545</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6025,7 +6029,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6035,12 +6039,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6049,6 +6048,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55279-2025 artfynd.xlsx
+++ b/artfynd/A 55279-2025 artfynd.xlsx
@@ -2682,32 +2682,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129965762</v>
+        <v>129965750</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>573793</v>
+        <v>574018</v>
       </c>
       <c r="R21" t="n">
-        <v>6738585</v>
+        <v>6738616</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2761,7 +2761,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2780,7 +2779,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129965766</v>
+        <v>129965762</v>
       </c>
       <c r="B22" t="n">
         <v>79088</v>
@@ -2815,10 +2814,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574017</v>
+        <v>573793</v>
       </c>
       <c r="R22" t="n">
-        <v>6738609</v>
+        <v>6738585</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2878,32 +2877,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129965750</v>
+        <v>129965766</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2913,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574018</v>
+        <v>574017</v>
       </c>
       <c r="R23" t="n">
-        <v>6738616</v>
+        <v>6738609</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2957,6 +2956,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129965753</v>
+        <v>129965763</v>
       </c>
       <c r="B31" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>573818</v>
+        <v>573855</v>
       </c>
       <c r="R31" t="n">
-        <v>6738603</v>
+        <v>6738592</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3735,6 +3735,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3753,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129965763</v>
+        <v>129965753</v>
       </c>
       <c r="B32" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3764,21 +3765,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3788,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>573855</v>
+        <v>573818</v>
       </c>
       <c r="R32" t="n">
-        <v>6738592</v>
+        <v>6738603</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3832,7 +3833,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129965734</v>
+        <v>130009803</v>
       </c>
       <c r="B42" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4831,40 +4831,45 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kojmyran, Dlr</t>
+          <t>Kojmyran Dlr, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>573877</v>
+        <v>573770</v>
       </c>
       <c r="R42" t="n">
-        <v>6738464</v>
+        <v>6738714</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4891,9 +4896,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4908,22 +4923,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130009803</v>
+        <v>129965734</v>
       </c>
       <c r="B43" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4931,45 +4946,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kojmyran Dlr, Dlr</t>
+          <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>573770</v>
+        <v>573877</v>
       </c>
       <c r="R43" t="n">
-        <v>6738714</v>
+        <v>6738464</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4996,19 +5006,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5023,12 +5023,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130009906</v>
+        <v>130009905</v>
       </c>
       <c r="B51" t="n">
-        <v>56930</v>
+        <v>91570</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5847,31 +5847,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5879,10 +5874,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>573857</v>
+        <v>573896</v>
       </c>
       <c r="R51" t="n">
-        <v>6738656</v>
+        <v>6738545</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5914,7 +5909,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5924,12 +5919,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5938,6 +5928,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5956,10 +5947,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130009905</v>
+        <v>130009906</v>
       </c>
       <c r="B52" t="n">
-        <v>91570</v>
+        <v>56930</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5967,26 +5958,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5994,10 +5990,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>573896</v>
+        <v>573857</v>
       </c>
       <c r="R52" t="n">
-        <v>6738545</v>
+        <v>6738656</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6029,7 +6025,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6039,7 +6035,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6048,7 +6049,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6183,10 +6183,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129965735</v>
+        <v>130009882</v>
       </c>
       <c r="B54" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6194,21 +6194,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6217,17 +6217,17 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kojmyran, Dlr</t>
+          <t>Kojmyran Dlr, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>573815</v>
+        <v>573810</v>
       </c>
       <c r="R54" t="n">
-        <v>6738469</v>
+        <v>6738459</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6254,65 +6254,89 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>I äldre björk</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130009895</v>
+        <v>130009815</v>
       </c>
       <c r="B55" t="n">
-        <v>78754</v>
+        <v>92888</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -6321,10 +6345,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>573923</v>
+        <v>573896</v>
       </c>
       <c r="R55" t="n">
-        <v>6738609</v>
+        <v>6738426</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6356,7 +6380,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6366,7 +6390,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6394,10 +6418,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130009882</v>
+        <v>130009893</v>
       </c>
       <c r="B56" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6405,26 +6429,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6432,10 +6461,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>573810</v>
+        <v>573916</v>
       </c>
       <c r="R56" t="n">
-        <v>6738459</v>
+        <v>6738552</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6467,7 +6496,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6477,12 +6506,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>I äldre björk</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6491,7 +6515,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6510,59 +6533,51 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130009815</v>
+        <v>129965735</v>
       </c>
       <c r="B57" t="n">
-        <v>92888</v>
+        <v>79707</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kojmyran Dlr, Dlr</t>
+          <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>573896</v>
+        <v>573815</v>
       </c>
       <c r="R57" t="n">
-        <v>6738426</v>
+        <v>6738469</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6589,50 +6604,39 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130009893</v>
+        <v>130009895</v>
       </c>
       <c r="B58" t="n">
-        <v>57737</v>
+        <v>78754</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6640,31 +6644,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6672,10 +6671,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>573916</v>
+        <v>573923</v>
       </c>
       <c r="R58" t="n">
-        <v>6738552</v>
+        <v>6738609</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6707,7 +6706,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6717,7 +6716,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6726,6 +6725,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55279-2025 artfynd.xlsx
+++ b/artfynd/A 55279-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129965755</v>
       </c>
       <c r="B2" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129965760</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -990,57 +990,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129960414</v>
+        <v>129965757</v>
       </c>
       <c r="B5" t="n">
-        <v>97672</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573945</v>
+        <v>574070</v>
       </c>
       <c r="R5" t="n">
-        <v>6738585</v>
+        <v>6738621</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,19 +1058,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,60 +1075,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129965746</v>
+        <v>129960414</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>97689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573966</v>
+        <v>573945</v>
       </c>
       <c r="R6" t="n">
-        <v>6738665</v>
+        <v>6738585</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,9 +1164,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129965757</v>
+        <v>129965746</v>
       </c>
       <c r="B7" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574070</v>
+        <v>573966</v>
       </c>
       <c r="R7" t="n">
-        <v>6738621</v>
+        <v>6738665</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1303,7 +1303,7 @@
         <v>129960347</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>129959101</v>
       </c>
       <c r="B9" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>129965747</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>129959968</v>
       </c>
       <c r="B12" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129965751</v>
+        <v>129965771</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1880,7 +1880,7 @@
         <v>573627</v>
       </c>
       <c r="R13" t="n">
-        <v>6738845</v>
+        <v>6738750</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1921,6 +1921,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1939,32 +1940,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129965771</v>
+        <v>129965751</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,7 +1978,7 @@
         <v>573627</v>
       </c>
       <c r="R14" t="n">
-        <v>6738750</v>
+        <v>6738845</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2018,7 +2019,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>129965744</v>
       </c>
       <c r="B15" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>129959721</v>
       </c>
       <c r="B16" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>129965765</v>
       </c>
       <c r="B17" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>129960128</v>
       </c>
       <c r="B18" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129965758</v>
+        <v>129960228</v>
       </c>
       <c r="B19" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,37 +2480,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>573893</v>
+        <v>574033</v>
       </c>
       <c r="R19" t="n">
-        <v>6738674</v>
+        <v>6738647</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2537,9 +2546,19 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2554,22 +2573,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129960228</v>
+        <v>129965758</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,46 +2596,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574033</v>
+        <v>573893</v>
       </c>
       <c r="R20" t="n">
-        <v>6738647</v>
+        <v>6738674</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2643,19 +2653,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2670,44 +2670,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129965750</v>
+        <v>129965766</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574018</v>
+        <v>574017</v>
       </c>
       <c r="R21" t="n">
-        <v>6738616</v>
+        <v>6738609</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2761,6 +2761,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2782,7 +2783,7 @@
         <v>129965762</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,32 +2878,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129965766</v>
+        <v>129965750</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2912,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574017</v>
+        <v>574018</v>
       </c>
       <c r="R23" t="n">
-        <v>6738609</v>
+        <v>6738616</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2956,7 +2957,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>129965743</v>
       </c>
       <c r="B24" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>129965741</v>
       </c>
       <c r="B25" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>129965748</v>
       </c>
       <c r="B26" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>129965756</v>
       </c>
       <c r="B27" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129965764</v>
+        <v>129965745</v>
       </c>
       <c r="B28" t="n">
-        <v>79088</v>
+        <v>78847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3374,21 +3374,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>573898</v>
+        <v>574015</v>
       </c>
       <c r="R28" t="n">
-        <v>6738621</v>
+        <v>6738720</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3442,7 +3442,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3464,7 +3463,7 @@
         <v>129965768</v>
       </c>
       <c r="B29" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3559,10 +3558,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129965745</v>
+        <v>129965764</v>
       </c>
       <c r="B30" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,21 +3569,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3594,10 +3593,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574015</v>
+        <v>573898</v>
       </c>
       <c r="R30" t="n">
-        <v>6738720</v>
+        <v>6738621</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3638,6 +3637,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129965763</v>
+        <v>129965753</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>573855</v>
+        <v>573818</v>
       </c>
       <c r="R31" t="n">
-        <v>6738592</v>
+        <v>6738603</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3735,7 +3735,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3754,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129965753</v>
+        <v>129965763</v>
       </c>
       <c r="B32" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3765,21 +3764,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3788,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>573818</v>
+        <v>573855</v>
       </c>
       <c r="R32" t="n">
-        <v>6738603</v>
+        <v>6738592</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3833,6 +3832,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129965767</v>
+        <v>129965769</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>573893</v>
+        <v>573745</v>
       </c>
       <c r="R33" t="n">
-        <v>6738657</v>
+        <v>6738790</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3952,7 +3952,7 @@
         <v>129965770</v>
       </c>
       <c r="B34" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4047,10 +4047,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129965769</v>
+        <v>129965767</v>
       </c>
       <c r="B35" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>573745</v>
+        <v>573893</v>
       </c>
       <c r="R35" t="n">
-        <v>6738790</v>
+        <v>6738657</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4148,7 +4148,7 @@
         <v>130009885</v>
       </c>
       <c r="B36" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>130009812</v>
       </c>
       <c r="B38" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>130009809</v>
       </c>
       <c r="B39" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4603,10 +4603,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130009811</v>
+        <v>129965736</v>
       </c>
       <c r="B40" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4614,21 +4614,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4637,17 +4637,17 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kojmyran Dlr, Dlr</t>
+          <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>573888</v>
+        <v>574018</v>
       </c>
       <c r="R40" t="n">
-        <v>6738654</v>
+        <v>6738557</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4674,24 +4674,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Tyvärr tog jag inget foto</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4707,22 +4692,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129965736</v>
+        <v>130009811</v>
       </c>
       <c r="B41" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4730,21 +4715,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4753,17 +4738,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kojmyran, Dlr</t>
+          <t>Kojmyran Dlr, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574018</v>
+        <v>573888</v>
       </c>
       <c r="R41" t="n">
-        <v>6738557</v>
+        <v>6738654</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4790,9 +4775,24 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Tyvärr tog jag inget foto</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4808,12 +4808,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4938,7 +4938,7 @@
         <v>129965734</v>
       </c>
       <c r="B43" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>129965737</v>
       </c>
       <c r="B44" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>130009806</v>
       </c>
       <c r="B45" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>130009808</v>
       </c>
       <c r="B46" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130009880</v>
+        <v>130009802</v>
       </c>
       <c r="B47" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5396,26 +5396,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5423,10 +5428,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>573818</v>
+        <v>573934</v>
       </c>
       <c r="R47" t="n">
-        <v>6738607</v>
+        <v>6738551</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5458,7 +5463,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5468,7 +5473,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5477,7 +5482,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5609,10 +5613,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130009802</v>
+        <v>130009880</v>
       </c>
       <c r="B49" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5620,31 +5624,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5652,10 +5651,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>573934</v>
+        <v>573818</v>
       </c>
       <c r="R49" t="n">
-        <v>6738551</v>
+        <v>6738607</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5687,7 +5686,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5697,7 +5696,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5706,6 +5705,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>130009804</v>
       </c>
       <c r="B50" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>130009905</v>
       </c>
       <c r="B51" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>130009810</v>
       </c>
       <c r="B53" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,36 +6183,44 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130009882</v>
+        <v>130009815</v>
       </c>
       <c r="B54" t="n">
-        <v>79088</v>
+        <v>92905</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -6221,10 +6229,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>573810</v>
+        <v>573896</v>
       </c>
       <c r="R54" t="n">
-        <v>6738459</v>
+        <v>6738426</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6256,7 +6264,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6266,12 +6274,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>I äldre björk</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6299,45 +6302,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130009815</v>
+        <v>130009893</v>
       </c>
       <c r="B55" t="n">
-        <v>92888</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>573896</v>
+        <v>573916</v>
       </c>
       <c r="R55" t="n">
-        <v>6738426</v>
+        <v>6738552</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6399,7 +6399,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6418,10 +6417,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130009893</v>
+        <v>129965735</v>
       </c>
       <c r="B56" t="n">
-        <v>57737</v>
+        <v>79708</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6429,45 +6428,40 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kojmyran Dlr, Dlr</t>
+          <t>Kojmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>573916</v>
+        <v>573815</v>
       </c>
       <c r="R56" t="n">
-        <v>6738552</v>
+        <v>6738469</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6494,19 +6488,9 @@
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6521,22 +6505,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129965735</v>
+        <v>130009895</v>
       </c>
       <c r="B57" t="n">
-        <v>79707</v>
+        <v>78755</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6544,21 +6528,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6567,17 +6551,17 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kojmyran, Dlr</t>
+          <t>Kojmyran Dlr, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>573815</v>
+        <v>573923</v>
       </c>
       <c r="R57" t="n">
-        <v>6738469</v>
+        <v>6738609</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6604,39 +6588,50 @@
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130009895</v>
+        <v>130009882</v>
       </c>
       <c r="B58" t="n">
-        <v>78754</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6644,21 +6639,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6671,10 +6666,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>573923</v>
+        <v>573810</v>
       </c>
       <c r="R58" t="n">
-        <v>6738609</v>
+        <v>6738459</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6706,7 +6701,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6716,7 +6711,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>I äldre björk</t>
         </is>
       </c>
       <c r="AD58" t="b">
